--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323643</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323367</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323663</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323690</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,8 +1802,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127323749</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99272</v>
+        <v>99274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135867367</v>
       </c>
       <c r="B49" t="n">
-        <v>97602</v>
+        <v>97604</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135863433</v>
       </c>
       <c r="B51" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135838485</v>
       </c>
       <c r="B52" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>135869120</v>
       </c>
       <c r="B53" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>135838731</v>
       </c>
       <c r="B55" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>135838791</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>135839239</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>135839971</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>589057</v>
       </c>
       <c r="R58" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6561,7 +6561,7 @@
         <v>135840042</v>
       </c>
       <c r="B59" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>135841778</v>
       </c>
       <c r="B60" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>135842147</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>135842319</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>135844103</v>
       </c>
       <c r="B63" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>135844184</v>
       </c>
       <c r="B64" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>135844236</v>
       </c>
       <c r="B65" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>135850268</v>
       </c>
       <c r="B66" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>135850269</v>
       </c>
       <c r="B67" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>135858805</v>
       </c>
       <c r="B68" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859076</v>
       </c>
       <c r="B69" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135859773</v>
       </c>
       <c r="B70" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863058</v>
       </c>
       <c r="B71" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>135863207</v>
       </c>
       <c r="B72" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>135864413</v>
       </c>
       <c r="B73" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135864789</v>
       </c>
       <c r="B74" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>135865049</v>
       </c>
       <c r="B75" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>135845341</v>
       </c>
       <c r="B76" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>135850276</v>
       </c>
       <c r="B77" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>135865976</v>
       </c>
       <c r="B78" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>135843889</v>
       </c>
       <c r="B79" t="n">
-        <v>92059</v>
+        <v>92061</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135870518</v>
       </c>
       <c r="B80" t="n">
-        <v>92059</v>
+        <v>92061</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>135844139</v>
       </c>
       <c r="B81" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>135864758</v>
       </c>
       <c r="B82" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>135865875</v>
       </c>
       <c r="B83" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>135866472</v>
       </c>
       <c r="B84" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135869941</v>
       </c>
       <c r="B86" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>135866077</v>
       </c>
       <c r="B87" t="n">
-        <v>92880</v>
+        <v>92882</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>135861199</v>
       </c>
       <c r="B88" t="n">
-        <v>92400</v>
+        <v>92402</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>135857566</v>
       </c>
       <c r="B93" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>135867349</v>
       </c>
       <c r="B94" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135869598</v>
       </c>
       <c r="B95" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>135870284</v>
       </c>
       <c r="B96" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>135866644</v>
       </c>
       <c r="B97" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135866907</v>
       </c>
       <c r="B98" t="n">
-        <v>92032</v>
+        <v>92034</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>135845312</v>
       </c>
       <c r="B99" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>135846453</v>
       </c>
       <c r="B100" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>135850266</v>
       </c>
       <c r="B101" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>135859801</v>
       </c>
       <c r="B102" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>135860380</v>
       </c>
       <c r="B103" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860403</v>
       </c>
       <c r="B104" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>135860895</v>
       </c>
       <c r="B105" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>135863025</v>
       </c>
       <c r="B106" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>135864806</v>
       </c>
       <c r="B107" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>589142</v>
       </c>
       <c r="R158" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -24726,7 +24726,7 @@
         <v>589142</v>
       </c>
       <c r="R234" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S234" t="n">
         <v>15</v>
@@ -29376,7 +29376,7 @@
         <v>135856895</v>
       </c>
       <c r="B277" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>135856870</v>
       </c>
       <c r="B278" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>135857313</v>
       </c>
       <c r="B279" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>135839938</v>
       </c>
       <c r="B282" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>135841204</v>
       </c>
       <c r="B283" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>135841251</v>
       </c>
       <c r="B284" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>135844085</v>
       </c>
       <c r="B285" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>135844774</v>
       </c>
       <c r="B286" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>135845274</v>
       </c>
       <c r="B287" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>135845458</v>
       </c>
       <c r="B288" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>135857308</v>
       </c>
       <c r="B289" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>135858017</v>
       </c>
       <c r="B290" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>135858106</v>
       </c>
       <c r="B291" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>135858631</v>
       </c>
       <c r="B292" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>135859788</v>
       </c>
       <c r="B293" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>135860011</v>
       </c>
       <c r="B294" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>135860130</v>
       </c>
       <c r="B295" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>135860668</v>
       </c>
       <c r="B296" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>135863056</v>
       </c>
       <c r="B297" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>135863790</v>
       </c>
       <c r="B298" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>135864635</v>
       </c>
       <c r="B299" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>135864833</v>
       </c>
       <c r="B300" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>135866243</v>
       </c>
       <c r="B301" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>135867025</v>
       </c>
       <c r="B302" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>135868685</v>
       </c>
       <c r="B303" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>135869575</v>
       </c>
       <c r="B304" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135870113</v>
       </c>
       <c r="B305" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>135870199</v>
       </c>
       <c r="B306" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>135870459</v>
       </c>
       <c r="B307" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>135879816</v>
       </c>
       <c r="B308" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>135840334</v>
       </c>
       <c r="B309" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>135860341</v>
       </c>
       <c r="B310" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>135864246</v>
       </c>
       <c r="B311" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>135864056</v>
       </c>
       <c r="B312" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>135839356</v>
       </c>
       <c r="B333" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>135842385</v>
       </c>
       <c r="B334" t="n">
-        <v>92396</v>
+        <v>92398</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -6280,7 +6280,7 @@
         <v>589057</v>
       </c>
       <c r="R56" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -16052,7 +16052,7 @@
         <v>589142</v>
       </c>
       <c r="R150" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -23593,7 +23593,7 @@
         <v>589142</v>
       </c>
       <c r="R223" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -27548,7 +27548,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Daniel Rutschman, Kim Hultgren</t>
+          <t>Erland Lindblad, Kim Hultgren, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>92865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99291</v>
+        <v>99292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92897</v>
+        <v>92898</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92414</v>
+        <v>92415</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75457</v>
+        <v>75458</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77071</v>
+        <v>77072</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92866</v>
+        <v>92867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92733</v>
+        <v>92734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91603</v>
+        <v>91604</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91603</v>
+        <v>91604</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92899</v>
+        <v>92900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97405</v>
+        <v>97406</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97405</v>
+        <v>97406</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>135839191</v>
       </c>
       <c r="B251" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>135840320</v>
       </c>
       <c r="B252" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>135841452</v>
       </c>
       <c r="B253" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>135845487</v>
       </c>
       <c r="B254" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>135860019</v>
       </c>
       <c r="B255" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>135861257</v>
       </c>
       <c r="B256" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>135861815</v>
       </c>
       <c r="B257" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>135862454</v>
       </c>
       <c r="B258" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>135862813</v>
       </c>
       <c r="B259" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>135864221</v>
       </c>
       <c r="B260" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>135864598</v>
       </c>
       <c r="B261" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>135870456</v>
       </c>
       <c r="B262" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>135844397</v>
       </c>
       <c r="B272" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>135859797</v>
       </c>
       <c r="B273" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>135844584</v>
       </c>
       <c r="B275" t="n">
-        <v>56546</v>
+        <v>56547</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75458</v>
+        <v>75459</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77072</v>
+        <v>77073</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92412</v>
+        <v>92413</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92412</v>
+        <v>92413</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92867</v>
+        <v>92873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92734</v>
+        <v>92740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91604</v>
+        <v>91610</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91604</v>
+        <v>91610</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96619</v>
+        <v>96625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92078</v>
+        <v>92084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92078</v>
+        <v>92084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92900</v>
+        <v>92906</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92417</v>
+        <v>92423</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97406</v>
+        <v>97412</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97406</v>
+        <v>97412</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92051</v>
+        <v>92057</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>135839191</v>
       </c>
       <c r="B251" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>135840320</v>
       </c>
       <c r="B252" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>135841452</v>
       </c>
       <c r="B253" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>135845487</v>
       </c>
       <c r="B254" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>135860019</v>
       </c>
       <c r="B255" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>135861257</v>
       </c>
       <c r="B256" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>135861815</v>
       </c>
       <c r="B257" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>135862454</v>
       </c>
       <c r="B258" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>135862813</v>
       </c>
       <c r="B259" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>135864221</v>
       </c>
       <c r="B260" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>135864598</v>
       </c>
       <c r="B261" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>135870456</v>
       </c>
       <c r="B262" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>135844397</v>
       </c>
       <c r="B272" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>135859797</v>
       </c>
       <c r="B273" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>135844584</v>
       </c>
       <c r="B275" t="n">
-        <v>56547</v>
+        <v>56551</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75459</v>
+        <v>75463</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77073</v>
+        <v>77077</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92413</v>
+        <v>92419</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92413</v>
+        <v>92419</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92873</v>
+        <v>92874</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99300</v>
+        <v>99301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91610</v>
+        <v>91611</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91610</v>
+        <v>91611</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96625</v>
+        <v>96626</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92084</v>
+        <v>92085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92084</v>
+        <v>92085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92906</v>
+        <v>92907</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92423</v>
+        <v>92424</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92057</v>
+        <v>92058</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>135839191</v>
       </c>
       <c r="B251" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>135840320</v>
       </c>
       <c r="B252" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>135841452</v>
       </c>
       <c r="B253" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>135845487</v>
       </c>
       <c r="B254" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>135860019</v>
       </c>
       <c r="B255" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>135861257</v>
       </c>
       <c r="B256" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>135861815</v>
       </c>
       <c r="B257" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>135862454</v>
       </c>
       <c r="B258" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>135862813</v>
       </c>
       <c r="B259" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>135864221</v>
       </c>
       <c r="B260" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>135864598</v>
       </c>
       <c r="B261" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>135870456</v>
       </c>
       <c r="B262" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>135844397</v>
       </c>
       <c r="B272" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>135859797</v>
       </c>
       <c r="B273" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>135844584</v>
       </c>
       <c r="B275" t="n">
-        <v>56551</v>
+        <v>56552</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75463</v>
+        <v>75464</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77077</v>
+        <v>77078</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92874</v>
+        <v>92880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99301</v>
+        <v>99312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91611</v>
+        <v>91617</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91611</v>
+        <v>91617</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96626</v>
+        <v>96637</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92085</v>
+        <v>92091</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92085</v>
+        <v>92091</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101486</v>
+        <v>101497</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92907</v>
+        <v>92913</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92424</v>
+        <v>92430</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97413</v>
+        <v>97424</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97413</v>
+        <v>97424</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92058</v>
+        <v>92064</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98324</v>
+        <v>98335</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75464</v>
+        <v>75468</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77078</v>
+        <v>77082</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92420</v>
+        <v>92426</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92420</v>
+        <v>92426</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92880</v>
+        <v>92887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92747</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99312</v>
+        <v>99325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91617</v>
+        <v>91624</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91617</v>
+        <v>91624</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96637</v>
+        <v>96650</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92091</v>
+        <v>92098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92091</v>
+        <v>92098</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101497</v>
+        <v>101510</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92913</v>
+        <v>92920</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92430</v>
+        <v>92437</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97424</v>
+        <v>97437</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97424</v>
+        <v>97437</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92064</v>
+        <v>92071</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80573</v>
+        <v>80579</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80573</v>
+        <v>80579</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>135839191</v>
       </c>
       <c r="B251" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>135840320</v>
       </c>
       <c r="B252" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>135841452</v>
       </c>
       <c r="B253" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>135845487</v>
       </c>
       <c r="B254" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>135860019</v>
       </c>
       <c r="B255" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>135861257</v>
       </c>
       <c r="B256" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>135861815</v>
       </c>
       <c r="B257" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>135862454</v>
       </c>
       <c r="B258" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>135862813</v>
       </c>
       <c r="B259" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>135864221</v>
       </c>
       <c r="B260" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>135864598</v>
       </c>
       <c r="B261" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>135870456</v>
       </c>
       <c r="B262" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>135844397</v>
       </c>
       <c r="B272" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>135859797</v>
       </c>
       <c r="B273" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>135844584</v>
       </c>
       <c r="B275" t="n">
-        <v>56552</v>
+        <v>56557</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98335</v>
+        <v>98348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75468</v>
+        <v>75474</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77082</v>
+        <v>77088</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92426</v>
+        <v>92433</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92426</v>
+        <v>92433</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92707</v>
+        <v>92708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99325</v>
+        <v>99326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92803</v>
+        <v>92804</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92803</v>
+        <v>92804</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96650</v>
+        <v>96651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101510</v>
+        <v>101511</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92920</v>
+        <v>92921</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92437</v>
+        <v>92438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97437</v>
+        <v>97438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97437</v>
+        <v>97438</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92071</v>
+        <v>92072</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042846</v>
+        <v>7042847</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92433</v>
+        <v>92434</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92433</v>
+        <v>92434</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135839464</v>
       </c>
       <c r="B2" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135839824</v>
       </c>
       <c r="B3" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135840421</v>
       </c>
       <c r="B4" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135844270</v>
       </c>
       <c r="B5" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92708</v>
+        <v>92721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135844958</v>
       </c>
       <c r="B8" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92888</v>
+        <v>92901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92755</v>
+        <v>92768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135843447</v>
       </c>
       <c r="B17" t="n">
-        <v>99326</v>
+        <v>99339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>135839300</v>
       </c>
       <c r="B20" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>135839967</v>
       </c>
       <c r="B21" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,7 +2727,7 @@
         <v>135840029</v>
       </c>
       <c r="B22" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135842210</v>
       </c>
       <c r="B23" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135843885</v>
       </c>
       <c r="B24" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135844114</v>
       </c>
       <c r="B25" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>135844280</v>
       </c>
       <c r="B26" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135845301</v>
       </c>
       <c r="B27" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135845938</v>
       </c>
       <c r="B28" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135838738</v>
       </c>
       <c r="B45" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135846473</v>
       </c>
       <c r="B46" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91625</v>
+        <v>91638</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91625</v>
+        <v>91638</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>135846370</v>
       </c>
       <c r="B49" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96651</v>
+        <v>96664</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135838485</v>
       </c>
       <c r="B51" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>135838731</v>
       </c>
       <c r="B54" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135838791</v>
       </c>
       <c r="B55" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135839239</v>
       </c>
       <c r="B56" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135839971</v>
       </c>
       <c r="B57" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042800</v>
+        <v>7042799</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6449,7 +6449,7 @@
         <v>135840042</v>
       </c>
       <c r="B58" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>135841778</v>
       </c>
       <c r="B59" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135842147</v>
       </c>
       <c r="B60" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>135842319</v>
       </c>
       <c r="B61" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>135844103</v>
       </c>
       <c r="B62" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135844184</v>
       </c>
       <c r="B63" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>135844236</v>
       </c>
       <c r="B64" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>135845341</v>
       </c>
       <c r="B75" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135843889</v>
       </c>
       <c r="B78" t="n">
-        <v>92099</v>
+        <v>92112</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92099</v>
+        <v>92112</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135844139</v>
       </c>
       <c r="B80" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101511</v>
+        <v>101524</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92921</v>
+        <v>92934</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92438</v>
+        <v>92451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97438</v>
+        <v>97451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97438</v>
+        <v>97451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92072</v>
+        <v>92085</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>135845312</v>
       </c>
       <c r="B98" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>135846453</v>
       </c>
       <c r="B99" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>135838376</v>
       </c>
       <c r="B108" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>135838435</v>
       </c>
       <c r="B109" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>135838467</v>
       </c>
       <c r="B110" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>135838765</v>
       </c>
       <c r="B111" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135839903</v>
       </c>
       <c r="B112" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>135840155</v>
       </c>
       <c r="B113" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>135840482</v>
       </c>
       <c r="B114" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>135841927</v>
       </c>
       <c r="B115" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>135844387</v>
       </c>
       <c r="B116" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>135845386</v>
       </c>
       <c r="B117" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>135845735</v>
       </c>
       <c r="B118" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>135845800</v>
       </c>
       <c r="B119" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135845874</v>
       </c>
       <c r="B120" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>135846153</v>
       </c>
       <c r="B121" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>135846717</v>
       </c>
       <c r="B122" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>135838954</v>
       </c>
       <c r="B141" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>135839959</v>
       </c>
       <c r="B142" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>135842099</v>
       </c>
       <c r="B143" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>135838382</v>
       </c>
       <c r="B155" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>135838407</v>
       </c>
       <c r="B156" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>135838455</v>
       </c>
       <c r="B157" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>135838515</v>
       </c>
       <c r="B158" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>135838541</v>
       </c>
       <c r="B159" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>135838859</v>
       </c>
       <c r="B160" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>135839011</v>
       </c>
       <c r="B161" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>135839142</v>
       </c>
       <c r="B162" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135839564</v>
       </c>
       <c r="B163" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>135840378</v>
       </c>
       <c r="B164" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>135840431</v>
       </c>
       <c r="B165" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>135840585</v>
       </c>
       <c r="B166" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>135840682</v>
       </c>
       <c r="B167" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>135841048</v>
       </c>
       <c r="B168" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>135841059</v>
       </c>
       <c r="B169" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>135841092</v>
       </c>
       <c r="B170" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>135841321</v>
       </c>
       <c r="B171" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>135841508</v>
       </c>
       <c r="B172" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>135841548</v>
       </c>
       <c r="B173" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>135841572</v>
       </c>
       <c r="B174" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>135841737</v>
       </c>
       <c r="B175" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>135841906</v>
       </c>
       <c r="B176" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>135842020</v>
       </c>
       <c r="B177" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>135842106</v>
       </c>
       <c r="B178" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>135842219</v>
       </c>
       <c r="B179" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>135842282</v>
       </c>
       <c r="B180" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>135842448</v>
       </c>
       <c r="B181" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>135843745</v>
       </c>
       <c r="B182" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>135843811</v>
       </c>
       <c r="B183" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>135843894</v>
       </c>
       <c r="B184" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>135844160</v>
       </c>
       <c r="B185" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>135844351</v>
       </c>
       <c r="B186" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>135844378</v>
       </c>
       <c r="B187" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>135844498</v>
       </c>
       <c r="B188" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>135844558</v>
       </c>
       <c r="B189" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135844859</v>
       </c>
       <c r="B190" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>135845357</v>
       </c>
       <c r="B191" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>135845439</v>
       </c>
       <c r="B192" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>135845497</v>
       </c>
       <c r="B193" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>135845502</v>
       </c>
       <c r="B194" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>135845716</v>
       </c>
       <c r="B195" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>135845782</v>
       </c>
       <c r="B196" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>135845848</v>
       </c>
       <c r="B197" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>135846113</v>
       </c>
       <c r="B198" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80579</v>
+        <v>80592</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80579</v>
+        <v>80592</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>135838386</v>
       </c>
       <c r="B232" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>135838463</v>
       </c>
       <c r="B233" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>135840594</v>
       </c>
       <c r="B234" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>135841605</v>
       </c>
       <c r="B235" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135842223</v>
       </c>
       <c r="B236" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>135844937</v>
       </c>
       <c r="B237" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>135838525</v>
       </c>
       <c r="B241" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>135840621</v>
       </c>
       <c r="B242" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>135841511</v>
       </c>
       <c r="B243" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>135844505</v>
       </c>
       <c r="B244" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>135841344</v>
       </c>
       <c r="B245" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>135841515</v>
       </c>
       <c r="B246" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>135839191</v>
       </c>
       <c r="B251" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>135840320</v>
       </c>
       <c r="B252" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>135841452</v>
       </c>
       <c r="B253" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>135845487</v>
       </c>
       <c r="B254" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>135860019</v>
       </c>
       <c r="B255" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>135861257</v>
       </c>
       <c r="B256" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>135861815</v>
       </c>
       <c r="B257" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>135862454</v>
       </c>
       <c r="B258" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>135862813</v>
       </c>
       <c r="B259" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>135864221</v>
       </c>
       <c r="B260" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>135864598</v>
       </c>
       <c r="B261" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>135870456</v>
       </c>
       <c r="B262" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>135844397</v>
       </c>
       <c r="B272" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>135859797</v>
       </c>
       <c r="B273" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>135844584</v>
       </c>
       <c r="B275" t="n">
-        <v>56557</v>
+        <v>56570</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98349</v>
+        <v>98362</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>135839938</v>
       </c>
       <c r="B281" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>135841204</v>
       </c>
       <c r="B282" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>135841251</v>
       </c>
       <c r="B283" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>135844085</v>
       </c>
       <c r="B284" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>135844774</v>
       </c>
       <c r="B285" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>135845274</v>
       </c>
       <c r="B286" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>135845458</v>
       </c>
       <c r="B287" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>135840334</v>
       </c>
       <c r="B308" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>135841306</v>
       </c>
       <c r="B312" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>135841732</v>
       </c>
       <c r="B313" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>135844359</v>
       </c>
       <c r="B314" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>135845853</v>
       </c>
       <c r="B315" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>135846119</v>
       </c>
       <c r="B316" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75474</v>
+        <v>75487</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77088</v>
+        <v>77101</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>135839356</v>
       </c>
       <c r="B332" t="n">
-        <v>92434</v>
+        <v>92447</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>135842385</v>
       </c>
       <c r="B333" t="n">
-        <v>92434</v>
+        <v>92447</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -2660,7 +2660,7 @@
         <v>589057</v>
       </c>
       <c r="R21" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -6382,7 +6382,7 @@
         <v>589057</v>
       </c>
       <c r="R57" t="n">
-        <v>7042799</v>
+        <v>7042800</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -16767,7 +16767,7 @@
         <v>589142</v>
       </c>
       <c r="R157" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -24614,7 +24614,7 @@
         <v>589142</v>
       </c>
       <c r="R233" t="n">
-        <v>7042847</v>
+        <v>7042846</v>
       </c>
       <c r="S233" t="n">
         <v>15</v>

--- a/artfynd/A 31917-2026 artfynd.xlsx
+++ b/artfynd/A 31917-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>135867199</v>
       </c>
       <c r="B6" t="n">
-        <v>92721</v>
+        <v>92722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135867391</v>
       </c>
       <c r="B7" t="n">
-        <v>92721</v>
+        <v>92722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135865862</v>
       </c>
       <c r="B9" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135866662</v>
       </c>
       <c r="B10" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135867221</v>
       </c>
       <c r="B11" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135869426</v>
       </c>
       <c r="B12" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135862438</v>
       </c>
       <c r="B13" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135862602</v>
       </c>
       <c r="B14" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135866065</v>
       </c>
       <c r="B15" t="n">
-        <v>92901</v>
+        <v>92902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135868496</v>
       </c>
       <c r="B16" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>135850271</v>
       </c>
       <c r="B29" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135859808</v>
       </c>
       <c r="B30" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>135859944</v>
       </c>
       <c r="B31" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>135860374</v>
       </c>
       <c r="B32" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135860415</v>
       </c>
       <c r="B33" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>135863044</v>
       </c>
       <c r="B34" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135863050</v>
       </c>
       <c r="B35" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135863211</v>
       </c>
       <c r="B36" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135864772</v>
       </c>
       <c r="B37" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135865803</v>
       </c>
       <c r="B38" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135867151</v>
       </c>
       <c r="B39" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135867394</v>
       </c>
       <c r="B40" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>135868983</v>
       </c>
       <c r="B41" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>135869135</v>
       </c>
       <c r="B42" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>135870175</v>
       </c>
       <c r="B43" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>135870547</v>
       </c>
       <c r="B44" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>135867294</v>
       </c>
       <c r="B47" t="n">
-        <v>91638</v>
+        <v>91639</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>135867315</v>
       </c>
       <c r="B48" t="n">
-        <v>91638</v>
+        <v>91639</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135863433</v>
       </c>
       <c r="B50" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>135869120</v>
       </c>
       <c r="B52" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>135850268</v>
       </c>
       <c r="B65" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>135850269</v>
       </c>
       <c r="B66" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>135858805</v>
       </c>
       <c r="B67" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135859076</v>
       </c>
       <c r="B68" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>135859773</v>
       </c>
       <c r="B69" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>135863058</v>
       </c>
       <c r="B70" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135863207</v>
       </c>
       <c r="B71" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>135864413</v>
       </c>
       <c r="B72" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>135864789</v>
       </c>
       <c r="B73" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>135865049</v>
       </c>
       <c r="B74" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>135850276</v>
       </c>
       <c r="B76" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135865976</v>
       </c>
       <c r="B77" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135870518</v>
       </c>
       <c r="B79" t="n">
-        <v>92112</v>
+        <v>92113</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>135864758</v>
       </c>
       <c r="B81" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>135865875</v>
       </c>
       <c r="B82" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>135866472</v>
       </c>
       <c r="B83" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>135869191</v>
       </c>
       <c r="B84" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>135869941</v>
       </c>
       <c r="B85" t="n">
-        <v>101524</v>
+        <v>101525</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135866077</v>
       </c>
       <c r="B86" t="n">
-        <v>92934</v>
+        <v>92935</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>135861199</v>
       </c>
       <c r="B87" t="n">
-        <v>92451</v>
+        <v>92452</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135857485</v>
       </c>
       <c r="B89" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>135862874</v>
       </c>
       <c r="B90" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>135863133</v>
       </c>
       <c r="B91" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>135857566</v>
       </c>
       <c r="B92" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>135867349</v>
       </c>
       <c r="B93" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>135869598</v>
       </c>
       <c r="B94" t="n">
-        <v>97451</v>
+        <v>97452</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>135870284</v>
       </c>
       <c r="B95" t="n">
-        <v>97451</v>
+        <v>97452</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135866644</v>
       </c>
       <c r="B96" t="n">
-        <v>92326</v>
+        <v>92327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135866907</v>
       </c>
       <c r="B97" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>135850266</v>
       </c>
       <c r="B100" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>135859801</v>
       </c>
       <c r="B101" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>135860380</v>
       </c>
       <c r="B102" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135860403</v>
       </c>
       <c r="B103" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135860895</v>
       </c>
       <c r="B104" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>135863025</v>
       </c>
       <c r="B105" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>135864806</v>
       </c>
       <c r="B106" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135850277</v>
       </c>
       <c r="B123" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>135850278</v>
       </c>
       <c r="B124" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>135859568</v>
       </c>
       <c r="B125" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>135859641</v>
       </c>
       <c r="B126" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>135860642</v>
       </c>
       <c r="B127" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>135860886</v>
       </c>
       <c r="B128" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>135861022</v>
       </c>
       <c r="B129" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>135861215</v>
       </c>
       <c r="B130" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>135862551</v>
       </c>
       <c r="B131" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>135862552</v>
       </c>
       <c r="B132" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>135862736</v>
       </c>
       <c r="B133" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>135862758</v>
       </c>
       <c r="B134" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>135867010</v>
       </c>
       <c r="B135" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>135867160</v>
       </c>
       <c r="B136" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>135869343</v>
       </c>
       <c r="B137" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>135869522</v>
       </c>
       <c r="B138" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>135879818</v>
       </c>
       <c r="B139" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>135862663</v>
       </c>
       <c r="B140" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>135859567</v>
       </c>
       <c r="B144" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>135859658</v>
       </c>
       <c r="B145" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>135862717</v>
       </c>
       <c r="B146" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>135867364</v>
       </c>
       <c r="B147" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>135862457</v>
       </c>
       <c r="B148" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>135862482</v>
       </c>
       <c r="B149" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>135861877</v>
       </c>
       <c r="B150" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>135865623</v>
       </c>
       <c r="B151" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>135866123</v>
       </c>
       <c r="B152" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>135850273</v>
       </c>
       <c r="B199" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>135850274</v>
       </c>
       <c r="B200" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>135850275</v>
       </c>
       <c r="B201" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>135858681</v>
       </c>
       <c r="B202" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>135859535</v>
       </c>
       <c r="B203" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>135859612</v>
       </c>
       <c r="B204" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>135859771</v>
       </c>
       <c r="B205" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>135861184</v>
       </c>
       <c r="B206" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>135861251</v>
       </c>
       <c r="B207" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135861277</v>
       </c>
       <c r="B208" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>135862888</v>
       </c>
       <c r="B209" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>135862901</v>
       </c>
       <c r="B210" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>135863719</v>
       </c>
       <c r="B211" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>135863728</v>
       </c>
       <c r="B212" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>135864018</v>
       </c>
       <c r="B213" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>135864129</v>
       </c>
       <c r="B214" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>135864250</v>
       </c>
       <c r="B215" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>135864612</v>
       </c>
       <c r="B216" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>135864742</v>
       </c>
       <c r="B217" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135864852</v>
       </c>
       <c r="B218" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>135865690</v>
       </c>
       <c r="B219" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>135865804</v>
       </c>
       <c r="B220" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>135865926</v>
       </c>
       <c r="B221" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>135866578</v>
       </c>
       <c r="B222" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>135867098</v>
       </c>
       <c r="B223" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>135867122</v>
       </c>
       <c r="B224" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>135867265</v>
       </c>
       <c r="B225" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>135870519</v>
       </c>
       <c r="B226" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135870592</v>
       </c>
       <c r="B227" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>135879814</v>
       </c>
       <c r="B228" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>135861275</v>
       </c>
       <c r="B229" t="n">
-        <v>80592</v>
+        <v>80593</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>135862592</v>
       </c>
       <c r="B230" t="n">
-        <v>80592</v>
+        <v>80593</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>135863003</v>
       </c>
       <c r="B238" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>135863725</v>
       </c>
       <c r="B239" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>135859643</v>
       </c>
       <c r="B247" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>135862930</v>
       </c>
       <c r="B248" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>135864867</v>
       </c>
       <c r="B249" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>135862824</v>
       </c>
       <c r="B250" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>135856895</v>
       </c>
       <c r="B276" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>135856870</v>
       </c>
       <c r="B277" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>135857313</v>
       </c>
       <c r="B278" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>135857308</v>
       </c>
       <c r="B288" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>135858017</v>
       </c>
       <c r="B289" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>135858106</v>
       </c>
       <c r="B290" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>135858631</v>
       </c>
       <c r="B291" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>135859788</v>
       </c>
       <c r="B292" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>135860011</v>
       </c>
       <c r="B293" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>135860130</v>
       </c>
       <c r="B294" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>135860668</v>
       </c>
       <c r="B295" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>135863056</v>
       </c>
       <c r="B296" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>135863790</v>
       </c>
       <c r="B297" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>135864635</v>
       </c>
       <c r="B298" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>135864833</v>
       </c>
       <c r="B299" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>135866243</v>
       </c>
       <c r="B300" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>135867025</v>
       </c>
       <c r="B301" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>135868685</v>
       </c>
       <c r="B302" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>135869575</v>
       </c>
       <c r="B303" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>135870113</v>
       </c>
       <c r="B304" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>135870199</v>
       </c>
       <c r="B305" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>135870459</v>
       </c>
       <c r="B306" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>135879816</v>
       </c>
       <c r="B307" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>135860341</v>
       </c>
       <c r="B309" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>135864246</v>
       </c>
       <c r="B310" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>135864056</v>
       </c>
       <c r="B311" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>135864257</v>
       </c>
       <c r="B317" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>135864860</v>
       </c>
       <c r="B318" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>135865910</v>
       </c>
       <c r="B319" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>135838722</v>
       </c>
       <c r="B320" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>135839052</v>
       </c>
       <c r="B321" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>135839215</v>
       </c>
       <c r="B322" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>135863127</v>
       </c>
       <c r="B323" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>135864126</v>
       </c>
       <c r="B324" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>135866016</v>
       </c>
       <c r="B325" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135866023</v>
       </c>
       <c r="B326" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>135866114</v>
       </c>
       <c r="B327" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>135867119</v>
       </c>
       <c r="B328" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>135879813</v>
       </c>
       <c r="B329" t="n">
-        <v>75487</v>
+        <v>75488</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>135862479</v>
       </c>
       <c r="B330" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>135886946</v>
       </c>
       <c r="B331" t="n">
-        <v>77101</v>
+        <v>77102</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
